--- a/prerun/data/example_file/fake.xlsx
+++ b/prerun/data/example_file/fake.xlsx
@@ -21,16 +21,16 @@
     <t xml:space="preserve">GCA</t>
   </si>
   <si>
-    <t xml:space="preserve">Content Area</t>
+    <t xml:space="preserve">Content.Area</t>
   </si>
   <si>
-    <t xml:space="preserve">Grade Group</t>
+    <t xml:space="preserve">Grade.Group</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of Tables per Room</t>
+    <t xml:space="preserve">Number.of.Tables.per.Room</t>
   </si>
   <si>
-    <t xml:space="preserve">Level Options</t>
+    <t xml:space="preserve">Level.Options</t>
   </si>
   <si>
     <t xml:space="preserve">SD</t>
@@ -327,283 +327,283 @@
     <t xml:space="preserve">ALD</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_1</t>
+    <t xml:space="preserve">item1</t>
   </si>
   <si>
     <t xml:space="preserve">Level1</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_2</t>
+    <t xml:space="preserve">item2</t>
   </si>
   <si>
     <t xml:space="preserve">Level2</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_3</t>
+    <t xml:space="preserve">item3</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_4</t>
+    <t xml:space="preserve">item4</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_5</t>
+    <t xml:space="preserve">item5</t>
   </si>
   <si>
     <t xml:space="preserve">Level3</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_6</t>
+    <t xml:space="preserve">item6</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_7</t>
+    <t xml:space="preserve">item7</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_8</t>
+    <t xml:space="preserve">item8</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_9</t>
+    <t xml:space="preserve">item9</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_10</t>
+    <t xml:space="preserve">item10</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_11</t>
+    <t xml:space="preserve">item11</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_12</t>
+    <t xml:space="preserve">item12</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_13</t>
+    <t xml:space="preserve">item13</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_14</t>
+    <t xml:space="preserve">item14</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_15</t>
+    <t xml:space="preserve">item15</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_16</t>
+    <t xml:space="preserve">item16</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_17</t>
+    <t xml:space="preserve">item17</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_18</t>
+    <t xml:space="preserve">item18</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_19</t>
+    <t xml:space="preserve">item19</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_20</t>
+    <t xml:space="preserve">item20</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_21</t>
+    <t xml:space="preserve">item21</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_22</t>
+    <t xml:space="preserve">item22</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_23</t>
+    <t xml:space="preserve">item23</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_24</t>
+    <t xml:space="preserve">item24</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_25</t>
+    <t xml:space="preserve">item25</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_26</t>
+    <t xml:space="preserve">item26</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_27</t>
+    <t xml:space="preserve">item27</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_28</t>
+    <t xml:space="preserve">item28</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_29</t>
+    <t xml:space="preserve">item29</t>
   </si>
   <si>
-    <t xml:space="preserve">M1_30</t>
+    <t xml:space="preserve">item30</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_1</t>
+    <t xml:space="preserve">item31</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_2</t>
+    <t xml:space="preserve">item32</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_3</t>
+    <t xml:space="preserve">item33</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_4</t>
+    <t xml:space="preserve">item34</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_5</t>
+    <t xml:space="preserve">item35</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_6</t>
+    <t xml:space="preserve">item36</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_7</t>
+    <t xml:space="preserve">item37</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_8</t>
+    <t xml:space="preserve">item38</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_9</t>
+    <t xml:space="preserve">item39</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_10</t>
+    <t xml:space="preserve">item40</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_11</t>
+    <t xml:space="preserve">item41</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_12</t>
+    <t xml:space="preserve">item42</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_13</t>
+    <t xml:space="preserve">item43</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_14</t>
+    <t xml:space="preserve">item44</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_15</t>
+    <t xml:space="preserve">item45</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_16</t>
+    <t xml:space="preserve">item46</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_17</t>
+    <t xml:space="preserve">item47</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_18</t>
+    <t xml:space="preserve">item48</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_19</t>
+    <t xml:space="preserve">item49</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_20</t>
+    <t xml:space="preserve">item50</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_21</t>
+    <t xml:space="preserve">item51</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_22</t>
+    <t xml:space="preserve">item52</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_23</t>
+    <t xml:space="preserve">item53</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_24</t>
+    <t xml:space="preserve">item54</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_25</t>
+    <t xml:space="preserve">item55</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_26</t>
+    <t xml:space="preserve">item56</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_27</t>
+    <t xml:space="preserve">item57</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_28</t>
+    <t xml:space="preserve">item58</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_29</t>
+    <t xml:space="preserve">item59</t>
   </si>
   <si>
-    <t xml:space="preserve">M2_30</t>
+    <t xml:space="preserve">item60</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_1</t>
+    <t xml:space="preserve">item61</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_2</t>
+    <t xml:space="preserve">item62</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_3</t>
+    <t xml:space="preserve">item63</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_4</t>
+    <t xml:space="preserve">item64</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_5</t>
+    <t xml:space="preserve">item65</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_6</t>
+    <t xml:space="preserve">item66</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_7</t>
+    <t xml:space="preserve">item67</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_8</t>
+    <t xml:space="preserve">item68</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_9</t>
+    <t xml:space="preserve">item69</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_10</t>
+    <t xml:space="preserve">item70</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_11</t>
+    <t xml:space="preserve">item71</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_12</t>
+    <t xml:space="preserve">item72</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_13</t>
+    <t xml:space="preserve">item73</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_14</t>
+    <t xml:space="preserve">item74</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_15</t>
+    <t xml:space="preserve">item75</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_16</t>
+    <t xml:space="preserve">item76</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_17</t>
+    <t xml:space="preserve">item77</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_18</t>
+    <t xml:space="preserve">item78</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_19</t>
+    <t xml:space="preserve">item79</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_20</t>
+    <t xml:space="preserve">item80</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_21</t>
+    <t xml:space="preserve">item81</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_22</t>
+    <t xml:space="preserve">item82</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_23</t>
+    <t xml:space="preserve">item83</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_24</t>
+    <t xml:space="preserve">item84</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_25</t>
+    <t xml:space="preserve">item85</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_26</t>
+    <t xml:space="preserve">item86</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_27</t>
+    <t xml:space="preserve">item87</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_28</t>
+    <t xml:space="preserve">item88</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_29</t>
+    <t xml:space="preserve">item89</t>
   </si>
   <si>
-    <t xml:space="preserve">M3_30</t>
+    <t xml:space="preserve">item90</t>
   </si>
   <si>
     <t xml:space="preserve">Domain</t>
